--- a/pyrate_features_binning/model_8_syn_old_pyrate_features.xlsx
+++ b/pyrate_features_binning/model_8_syn_old_pyrate_features.xlsx
@@ -5,18 +5,29 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimoesLabAdmin\Documents\pt_diversity_rates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimoesLabAdmin\Documents\pt_diversity_rates\pyrate_features_binning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{502A8571-11F4-404B-9AFB-CD7037498518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE5F9D7-FBB7-42E3-A41C-3DDD3CB1F55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57750" yWindow="330" windowWidth="28770" windowHeight="15450" xr2:uid="{75BA9CC0-575C-4720-B405-A94ABBF381C0}"/>
+    <workbookView xWindow="54510" yWindow="2415" windowWidth="28440" windowHeight="12435" xr2:uid="{75BA9CC0-575C-4720-B405-A94ABBF381C0}"/>
   </bookViews>
   <sheets>
     <sheet name="model_8_syn_old_pyrate_features" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
